--- a/astro-site/public/dl/haccp-templates/12-haccp-plan-hazard-analysis.xlsx
+++ b/astro-site/public/dl/haccp-templates/12-haccp-plan-hazard-analysis.xlsx
@@ -717,7 +717,7 @@
     <row r="14">
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>▸ That is why allergen labeling at receiving and the allergen menu at service are listed as OPRP and not CCP: "complete label" and "up-to-date menu" are not measurable critical limits. The real allergen control is in the kitchen, and there it is a CCP.</t>
+          <t>▸ That is why allergen labeling at receiving and the allergen menu at service are listed as OPRP and not CCP: "complete label" and "up-to-date menu" are not measurable critical limits. The real allergen control is in the kitchen, managed as an OPRP with 100% compliance on every allergy order.</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Microbial growth from thawing at room temperature or under the tap</t>
+          <t>Microbial growth from thawing at room temperature, in standing water or under warm running water. Cold running water at 70 °F (21 °C) or below is allowed (§3-501.13(B))</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>In the cooler at ≤ 41 °F, covered and on a rack tray; use within 24 h of the START of thawing (house limit; this is what template 17 measures: it caps the total time in the temperature danger zone)</t>
+          <t>In the cooler at ≤ 41 °F, covered and on a rack tray; use within 24 h of the START of thawing (house limit; this is what template 17 measures)</t>
         </is>
       </c>
       <c r="J12" s="19" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L12" s="19" t="inlineStr">
         <is>
-          <t>Discard product thawed outside the cooler; open an incident in template 11 (Corrective Action Log)</t>
+          <t>Discard product thawed any other way than in the cooler or under cold running water at 70 °F (21 °C) or below (§3-501.13(B)); open an incident in template 11 (Corrective Action Log)</t>
         </is>
       </c>
       <c r="M12" s="19" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
-          <t>Free residual chlorine between 0.2 and 4.0 mg/L and water without cloudiness or abnormal color or smell (40 CFR 141.72 and 141.65)</t>
+          <t>Residual chlorine between 0.2 mg/L (entry-point minimum) and 4.0 mg/L, measured as total chlorine if your utility uses chloramine, and water without cloudiness or abnormal color or smell (40 CFR 141.72 and 141.65; in the distribution system a detectable residual is required)</t>
         </is>
       </c>
       <c r="J15" s="19" t="inlineStr">
